--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>healthCareFacility représente la structure de prise en charge (cabinet du médecin, hôpital ou clinique, etc.).</t>
+    <t>L'élément de l'en-tête du CDA healthCareFacility permet de représenter la structure de prise en charge (cabinet du médecin, hôpital ou clinique, etc.).</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
